--- a/artfynd/A 43927-2024 artfynd.xlsx
+++ b/artfynd/A 43927-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89564764</v>
+        <v>89564755</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399013.1904378039</v>
+        <v>399231</v>
       </c>
       <c r="R2" t="n">
-        <v>7084512.854551315</v>
+        <v>7084283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89564727</v>
+        <v>89564693</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399367.1658262271</v>
+        <v>399337</v>
       </c>
       <c r="R3" t="n">
-        <v>7083459.902836174</v>
+        <v>7083678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,21 +844,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +857,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89564742</v>
+        <v>89564776</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399269.8036996775</v>
+        <v>399374</v>
       </c>
       <c r="R4" t="n">
-        <v>7083770.991352688</v>
+        <v>7083461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,21 +950,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,6 +963,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Björkstubbe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1028,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89564776</v>
+        <v>89564767</v>
       </c>
       <c r="B5" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399373.8285079305</v>
+        <v>398963</v>
       </c>
       <c r="R5" t="n">
-        <v>7083461.012658826</v>
+        <v>7084526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,21 +1056,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,7 +1072,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Björkstubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89564729</v>
+        <v>89564616</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398997.0089555617</v>
+        <v>399176</v>
       </c>
       <c r="R6" t="n">
-        <v>7084504.113284101</v>
+        <v>7083873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,21 +1162,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1245,11 +1175,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89564695</v>
+        <v>89564777</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>399152.8082063479</v>
+        <v>398982</v>
       </c>
       <c r="R7" t="n">
-        <v>7083828.136009361</v>
+        <v>7084518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,21 +1263,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,11 +1276,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sten</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1391,15 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89564780</v>
+        <v>89564671</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398979.9858255244</v>
+        <v>399351</v>
       </c>
       <c r="R8" t="n">
-        <v>7084524.069655132</v>
+        <v>7083670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,19 +1364,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,37 +1397,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89564766</v>
+        <v>89564796</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>399213.7906670177</v>
+        <v>399123</v>
       </c>
       <c r="R9" t="n">
-        <v>7084034.844613435</v>
+        <v>7084417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,19 +1465,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,37 +1498,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89564761</v>
+        <v>89564676</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>399231.8075803516</v>
+        <v>399360</v>
       </c>
       <c r="R10" t="n">
-        <v>7084347.905906009</v>
+        <v>7083473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,19 +1566,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89564767</v>
+        <v>89564740</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1779,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398962.821650515</v>
+        <v>399361</v>
       </c>
       <c r="R11" t="n">
-        <v>7084525.946252307</v>
+        <v>7083664</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,21 +1667,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1835,11 +1680,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1860,37 +1700,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89564784</v>
+        <v>89564748</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>399040.1616517897</v>
+        <v>399164</v>
       </c>
       <c r="R12" t="n">
-        <v>7084500.076249678</v>
+        <v>7084407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,21 +1768,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1956,11 +1781,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1981,15 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89564788</v>
+        <v>89564766</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,21 +1812,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2021,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>399021.1615196676</v>
+        <v>399214</v>
       </c>
       <c r="R13" t="n">
-        <v>7084499.806255363</v>
+        <v>7084035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,19 +1869,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,15 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89564740</v>
+        <v>89564793</v>
       </c>
       <c r="B14" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>399360.9039035504</v>
+        <v>399058</v>
       </c>
       <c r="R14" t="n">
-        <v>7083663.944143057</v>
+        <v>7084473</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,19 +1970,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,15 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89564748</v>
+        <v>89564753</v>
       </c>
       <c r="B15" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,21 +2014,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>399163.9231125895</v>
+        <v>399040</v>
       </c>
       <c r="R15" t="n">
-        <v>7084406.991314468</v>
+        <v>7084500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,21 +2071,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2309,6 +2084,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2329,37 +2109,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89564671</v>
+        <v>89564791</v>
       </c>
       <c r="B16" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2813</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2369,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>399350.9374921879</v>
+        <v>399230</v>
       </c>
       <c r="R16" t="n">
-        <v>7083669.999691945</v>
+        <v>7084350</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2402,21 +2177,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2425,6 +2190,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2445,37 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89564676</v>
+        <v>89564695</v>
       </c>
       <c r="B17" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2485,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>399360.0732205217</v>
+        <v>399153</v>
       </c>
       <c r="R17" t="n">
-        <v>7083472.926067714</v>
+        <v>7083828</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,21 +2283,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2541,6 +2296,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2561,37 +2321,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89564791</v>
+        <v>89564729</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>399230.1135257166</v>
+        <v>398997</v>
       </c>
       <c r="R18" t="n">
-        <v>7084350.16589553</v>
+        <v>7084504</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,21 +2389,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2660,7 +2405,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Sten</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2682,37 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89564693</v>
+        <v>89564757</v>
       </c>
       <c r="B19" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>399337.0558598851</v>
+        <v>399068</v>
       </c>
       <c r="R19" t="n">
-        <v>7083677.945771553</v>
+        <v>7084460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,21 +2495,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2781,7 +2511,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2803,37 +2533,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89564796</v>
+        <v>89564764</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>399123.1736903663</v>
+        <v>399013</v>
       </c>
       <c r="R20" t="n">
-        <v>7084417.124647017</v>
+        <v>7084513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,21 +2601,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2899,6 +2614,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2919,37 +2639,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89564755</v>
+        <v>89564784</v>
       </c>
       <c r="B21" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2959,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>399231.0485167911</v>
+        <v>399040</v>
       </c>
       <c r="R21" t="n">
-        <v>7084283.087352304</v>
+        <v>7084500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,21 +2707,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3015,6 +2720,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3035,15 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89564777</v>
+        <v>89564780</v>
       </c>
       <c r="B22" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398981.9929737385</v>
+        <v>398980</v>
       </c>
       <c r="R22" t="n">
-        <v>7084517.829800689</v>
+        <v>7084524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3108,19 +2813,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,37 +2846,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89564661</v>
+        <v>89564761</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3191,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>399382.1293598152</v>
+        <v>399232</v>
       </c>
       <c r="R23" t="n">
-        <v>7083526.929554195</v>
+        <v>7084348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,19 +2914,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3267,37 +2947,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89564793</v>
+        <v>89564783</v>
       </c>
       <c r="B24" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3307,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>399057.8406127249</v>
+        <v>399163</v>
       </c>
       <c r="R24" t="n">
-        <v>7084473.041560546</v>
+        <v>7084408</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,21 +3015,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3363,6 +3028,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3376,485 +3046,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>89564616</v>
-      </c>
-      <c r="B25" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Källpraktmossa</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Pseudobryum cinclidioides</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>399175.8918986503</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7083872.834398908</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>89564757</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>399068.0180275786</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7084459.922173283</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>89564753</v>
-      </c>
-      <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>399040.1616517897</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7084500.076249678</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>89564783</v>
-      </c>
-      <c r="B28" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>229748</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gytterlav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Protopannaria pezizoides</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>399163.0690364379</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7084407.90098796</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Sten</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 43927-2024 artfynd.xlsx
+++ b/artfynd/A 43927-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564693</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564767</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564777</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564671</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564796</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564676</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564766</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564793</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564753</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564791</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564695</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,6 +2509,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564729</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2530,6 +2620,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2636,6 +2731,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564764</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2742,6 +2842,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564784</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2843,6 +2948,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564780</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564761</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3050,8 +3165,38 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564783</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>